--- a/Zinc/6. Statistical data analysis/Multiple linear regression/Simple_MLR.xlsx
+++ b/Zinc/6. Statistical data analysis/Multiple linear regression/Simple_MLR.xlsx
@@ -1,77 +1,87 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Zinc/6. Statistical data analysis/Multiple linear regression/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_C5797D5B4E75693BD60E26F920E03FA88AB48211" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C453BB5-7777-471D-8247-32988644C163}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Coefficients" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Model_Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Coefficients" sheetId="1" r:id="rId1"/>
+    <sheet name="Model_Summary" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
-    <t xml:space="preserve">Term</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Std. Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pr(&gt;|t|)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(Intercept)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Zn_nM_std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_DOC_nM_std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Ca_nM_std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residual standard error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R-squared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjusted R-squared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-statistic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numerator df</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denominator df</t>
+    <t>Term</t>
+  </si>
+  <si>
+    <t>Estimate</t>
+  </si>
+  <si>
+    <t>Std. Error</t>
+  </si>
+  <si>
+    <t>t value</t>
+  </si>
+  <si>
+    <t>Pr(&gt;|t|)</t>
+  </si>
+  <si>
+    <t>(Intercept)</t>
+  </si>
+  <si>
+    <t>log_Zn_nM_std</t>
+  </si>
+  <si>
+    <t>log_DOC_nM_std</t>
+  </si>
+  <si>
+    <t>log_Ca_nM_std</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Residual standard error</t>
+  </si>
+  <si>
+    <t>R-squared</t>
+  </si>
+  <si>
+    <t>Adjusted R-squared</t>
+  </si>
+  <si>
+    <t>F-statistic</t>
+  </si>
+  <si>
+    <t>Numerator df</t>
+  </si>
+  <si>
+    <t>Denominator df</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -100,14 +110,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -388,11 +413,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -409,86 +434,89 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="n">
-        <v>-0.0000000000000000792831043374616</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.0158473827004664</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.00000000000000500291472958043</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="B2">
+        <v>-7.9283104337461597E-17</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1.58473827004664E-2</v>
+      </c>
+      <c r="D2">
+        <v>-5.0029147295804299E-15</v>
+      </c>
+      <c r="E2">
         <v>0.999999999999996</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="n">
-        <v>0.904423467425729</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.0164490208242482</v>
-      </c>
-      <c r="D3" t="n">
-        <v>54.9834228486403</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000730220977362626</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="B3">
+        <v>0.90442346742572899</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1.6449020824248199E-2</v>
+      </c>
+      <c r="D3">
+        <v>54.983422848640302</v>
+      </c>
+      <c r="E3">
+        <v>7.3022097736262604E-175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="n">
-        <v>-0.437400625777796</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.0163856457164646</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-26.694134204201</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000132826934157894</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="B4">
+        <v>-0.43740062577779598</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1.63856457164646E-2</v>
+      </c>
+      <c r="D4">
+        <v>-26.694134204200999</v>
+      </c>
+      <c r="E4">
+        <v>1.32826934157894E-86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>-0.387768316623951</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.0160783315718684</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-24.1174474410276</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000147701469077189</v>
+      <c r="C5" s="2">
+        <v>1.6078331571868401E-2</v>
+      </c>
+      <c r="D5">
+        <v>-24.117447441027601</v>
+      </c>
+      <c r="E5">
+        <v>1.4770146907718901E-76</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.6328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -496,56 +524,56 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="n">
-        <v>0.299007818777361</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="B2" s="1">
+        <v>0.29900781877736099</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="n">
-        <v>0.911349865231329</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="B3">
+        <v>0.91134986523132899</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="n">
-        <v>0.910594324310005</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="B4">
+        <v>0.91059432431000498</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1206.22171415204</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>352</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Zinc/6. Statistical data analysis/Multiple linear regression/Simple_MLR.xlsx
+++ b/Zinc/6. Statistical data analysis/Multiple linear regression/Simple_MLR.xlsx
@@ -1,87 +1,77 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Zinc/6. Statistical data analysis/Multiple linear regression/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_C5797D5B4E75693BD60E26F920E03FA88AB48211" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C453BB5-7777-471D-8247-32988644C163}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Coefficients" sheetId="1" r:id="rId1"/>
-    <sheet name="Model_Summary" sheetId="2" r:id="rId2"/>
+    <sheet name="Coefficients" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Model_Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
-    <t>Term</t>
-  </si>
-  <si>
-    <t>Estimate</t>
-  </si>
-  <si>
-    <t>Std. Error</t>
-  </si>
-  <si>
-    <t>t value</t>
-  </si>
-  <si>
-    <t>Pr(&gt;|t|)</t>
-  </si>
-  <si>
-    <t>(Intercept)</t>
-  </si>
-  <si>
-    <t>log_Zn_nM_std</t>
-  </si>
-  <si>
-    <t>log_DOC_nM_std</t>
-  </si>
-  <si>
-    <t>log_Ca_nM_std</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Residual standard error</t>
-  </si>
-  <si>
-    <t>R-squared</t>
-  </si>
-  <si>
-    <t>Adjusted R-squared</t>
-  </si>
-  <si>
-    <t>F-statistic</t>
-  </si>
-  <si>
-    <t>Numerator df</t>
-  </si>
-  <si>
-    <t>Denominator df</t>
+    <t xml:space="preserve">Term</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Std. Error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pr(&gt;|t|)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Zn_nM_std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_DOC_nM_std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Ca_nM_std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residual standard error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-squared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjusted R-squared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-statistic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numerator df</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denominator df</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-  </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -110,29 +100,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,11 +388,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -434,89 +409,86 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
-        <v>-7.9283104337461597E-17</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1.58473827004664E-2</v>
-      </c>
-      <c r="D2">
-        <v>-5.0029147295804299E-15</v>
-      </c>
-      <c r="E2">
-        <v>0.999999999999996</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B2" t="n">
+        <v>-0.00000000000000161788369850036</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0156671184316724</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.000000000000103266194454091</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.999999999999918</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3">
-        <v>0.90442346742572899</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1.6449020824248199E-2</v>
-      </c>
-      <c r="D3">
-        <v>54.983422848640302</v>
-      </c>
-      <c r="E3">
-        <v>7.3022097736262604E-175</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B3" t="n">
+        <v>0.890605115905496</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0162377802069615</v>
+      </c>
+      <c r="D3" t="n">
+        <v>54.8477134530785</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000343361867873333</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4">
-        <v>-0.43740062577779598</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1.63856457164646E-2</v>
-      </c>
-      <c r="D4">
-        <v>-26.694134204200999</v>
-      </c>
-      <c r="E4">
-        <v>1.32826934157894E-86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B4" t="n">
+        <v>-0.469680801240599</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0161611600415066</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-29.0623197860995</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000835081870418051</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5">
-        <v>-0.387768316623951</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1.6078331571868401E-2</v>
-      </c>
-      <c r="D5">
-        <v>-24.117447441027601</v>
-      </c>
-      <c r="E5">
-        <v>1.4770146907718901E-76</v>
+      <c r="B5" t="n">
+        <v>-0.384752139951962</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.01579599651228</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-24.3575731137223</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000927401512015228</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="20.6328125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -524,56 +496,56 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1">
-        <v>0.29900781877736099</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B2" t="n">
+        <v>0.307810038142831</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3">
-        <v>0.91134986523132899</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B3" t="n">
+        <v>0.90599126888278</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="B4">
-        <v>0.91059432431000498</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" t="n">
+        <v>0.905252980418509</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="B5">
-        <v>1206.22171415204</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B5" t="n">
+        <v>1227.15078553602</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7">
-        <v>352</v>
+      <c r="B7" t="n">
+        <v>382</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>